--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
